--- a/data/trans_orig/ProbViv_temp-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/ProbViv_temp-Estudios-trans_orig.xlsx
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24336</t>
+          <t>23684</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40714</t>
+          <t>40284</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24493</t>
+          <t>24208</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38614</t>
+          <t>38690</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51924</t>
+          <t>51777</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75900</t>
+          <t>73758</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>63,21%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13964</t>
+          <t>14394</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30342</t>
+          <t>30994</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23390</t>
+          <t>23314</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37511</t>
+          <t>37796</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40782</t>
+          <t>42924</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64758</t>
+          <t>64905</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,63%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>187156</t>
+          <t>187790</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>258169</t>
+          <t>260602</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>176626</t>
+          <t>174721</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>219096</t>
+          <t>219375</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>376222</t>
+          <t>377097</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>465231</t>
+          <t>470952</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>48,2%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>202341</t>
+          <t>199908</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>273354</t>
+          <t>272720</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>297523</t>
+          <t>297244</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>339993</t>
+          <t>341898</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>511898</t>
+          <t>506177</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>600907</t>
+          <t>600032</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,41%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34143</t>
+          <t>34616</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53014</t>
+          <t>52771</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46622</t>
+          <t>46111</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70923</t>
+          <t>70307</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86242</t>
+          <t>86011</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117751</t>
+          <t>116363</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,16%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>95538</t>
+          <t>95781</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114409</t>
+          <t>113936</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111482</t>
+          <t>112098</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>135783</t>
+          <t>136294</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>213206</t>
+          <t>214594</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>244715</t>
+          <t>244946</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,01%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>257662</t>
+          <t>255816</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>343061</t>
+          <t>337523</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>259269</t>
+          <t>260623</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>310694</t>
+          <t>312103</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>531536</t>
+          <t>534249</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>626339</t>
+          <t>628480</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,11%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>320678</t>
+          <t>326216</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>406077</t>
+          <t>407923</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>450334</t>
+          <t>448925</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>501759</t>
+          <t>500405</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>798428</t>
+          <t>796287</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>893231</t>
+          <t>890518</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,5%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ProbViv_temp-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/ProbViv_temp-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,47 +836,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>56462</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1179,47 +1179,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>465</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>310317</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>465</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1522,47 +1522,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>136581</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1865,47 +1865,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2439,47 +2439,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>55484</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2782,47 +2782,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>441</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>304653</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>441</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3125,47 +3125,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>116827</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3468,47 +3468,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4042,47 +4042,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>40641</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4385,47 +4385,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>525</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>348722</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>525</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>348722</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>348722</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>348722</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4728,47 +4728,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>136027</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5071,47 +5071,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29838</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23271</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>35900</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>52,6%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>41,02%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>63,28%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>32256</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>23684</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>40284</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>58,99%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>43,32%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>73,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>31374</t>
+          <t>24148</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24208</t>
+          <t>18233</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38690</t>
+          <t>29987</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>63630</t>
+          <t>53987</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51777</t>
+          <t>44454</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73758</t>
+          <t>62458</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>60,35%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>26894</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20832</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>33461</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>47,4%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>36,72%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>58,98%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>22422</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14394</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>30994</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>41,01%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>26,32%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>56,68%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30630</t>
+          <t>22610</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23314</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37796</t>
+          <t>28525</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>53052</t>
+          <t>49503</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42924</t>
+          <t>41032</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64905</t>
+          <t>59036</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>57,05%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>189721</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>169216</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>211098</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>39,88%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>35,57%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>44,38%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>211052</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>187790</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>260602</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>45,83%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>40,78%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>56,59%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>198052</t>
+          <t>188302</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>174721</t>
+          <t>171423</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>219375</t>
+          <t>206001</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>409104</t>
+          <t>378024</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>377097</t>
+          <t>349216</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>470952</t>
+          <t>405183</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>44,62%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>285957</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>264580</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>306462</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>60,12%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>55,62%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>64,43%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>372</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>249458</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>199908</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>272720</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>54,17%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>43,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>59,22%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>318567</t>
+          <t>244146</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>297244</t>
+          <t>226447</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>341898</t>
+          <t>261025</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>568025</t>
+          <t>530102</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>506177</t>
+          <t>502943</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>600032</t>
+          <t>558910</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,55%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>50443</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>40858</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>61918</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>30,12%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>24,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>36,97%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>43256</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>34616</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>52771</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>29,12%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>23,3%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35,52%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>57363</t>
+          <t>42837</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46111</t>
+          <t>33421</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70307</t>
+          <t>52186</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>100619</t>
+          <t>93280</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86011</t>
+          <t>80178</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>116363</t>
+          <t>109331</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>117019</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>105544</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>126604</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>69,88%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>63,03%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>75,6%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>105296</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>95781</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>113936</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>70,88%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>64,48%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>76,7%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>125042</t>
+          <t>106064</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>112098</t>
+          <t>96715</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>136294</t>
+          <t>115480</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>230338</t>
+          <t>223082</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>214594</t>
+          <t>207031</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>244946</t>
+          <t>236184</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,66%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>148552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>148552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>148552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148901</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148901</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148901</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>330957</t>
+          <t>316362</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>330957</t>
+          <t>316362</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>330957</t>
+          <t>316362</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>270003</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>243222</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>292631</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>38,58%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>34,75%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>41,81%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>368</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>286563</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>255816</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>337523</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>43,17%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>38,54%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>50,85%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>286789</t>
+          <t>255287</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>260623</t>
+          <t>234411</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>312103</t>
+          <t>276460</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>573352</t>
+          <t>525290</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>534249</t>
+          <t>494173</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>628480</t>
+          <t>558557</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>42,06%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>429869</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>407241</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>456650</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>61,42%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>58,19%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>65,25%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>573</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>377176</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>326216</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>407923</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>56,83%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>49,15%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>61,46%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>474239</t>
+          <t>372819</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>448925</t>
+          <t>351646</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>500405</t>
+          <t>393695</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>851415</t>
+          <t>802688</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>796287</t>
+          <t>769421</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>890518</t>
+          <t>833805</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,79%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>663739</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>663739</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>663739</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628106</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628106</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628106</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1424767</t>
+          <t>1327978</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1424767</t>
+          <t>1327978</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1424767</t>
+          <t>1327978</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
